--- a/assets/constructions/examples/ctd_tsmb_back_boring.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_back_boring.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,69 +634,88 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M772BBR15L30L VBX</t>
+          <t>L080.0004-25/CN45F</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>DUEMMEL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microscope</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>VAR_M7</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+          <t>ULTRAMINI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMKS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.45</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.8</v>
+      </c>
       <c r="N2" t="n">
-        <v>6.95</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="P2" t="n">
+        <v>37.5</v>
+      </c>
       <c r="Q2" t="n">
-        <v>61</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
         <v>0.15</v>
@@ -706,16 +725,14 @@
           <t>L</t>
         </is>
       </c>
-      <c r="W2" t="n">
-        <v>34</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="AA2" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AB2" t="n">
         <v>30</v>
@@ -723,7 +740,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>VARGUS_D:7</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -733,12 +750,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>CN45F</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
@@ -760,14 +777,33 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>5503.15</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M662BBR15L30L VBX</t>
+          <t>M772BBR15L30L VBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -782,7 +818,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VAR_M6</t>
+          <t>VAR_M7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -797,35 +833,35 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>2.45</v>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>5.95</v>
+        <v>6.95</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
         <v>0.15</v>
@@ -836,7 +872,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>29.8</v>
+        <v>34</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -852,7 +888,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -890,13 +926,32 @@
       <c r="AO3" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>5125.3</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M552BBR15L30L VBX</t>
+          <t>M552BBR15L30R VBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -961,7 +1016,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1021,80 +1076,107 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
+        <v>3597.37</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L080.0004-15/CN45F</t>
+          <t>M662BBR15L14RVTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ULTRAMINI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>Microscope</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VAR_M6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.45</v>
+      </c>
       <c r="L5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.95</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>5.62</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
-      </c>
-      <c r="P5" t="n">
-        <v>27.5</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>29</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
         <v>0.15</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>18.3</v>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AA5" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB5" t="n">
         <v>30</v>
@@ -1102,7 +1184,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>DUEM_DCON:4</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1112,12 +1194,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>CN45F</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
@@ -1139,14 +1221,33 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Ultramini.pdf</t>
+          <t>2022 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>4378.8</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R080.0005-30/CN45F</t>
+          <t>L080.0004-15/CN45F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1168,44 +1269,44 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>43.5</v>
+        <v>27.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1223,7 +1324,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>DUEM_DCON:5</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1261,6 +1362,25 @@
       <c r="AO6" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
+        <v>4846.74</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
